--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125529623</v>
+        <v>125528826</v>
       </c>
       <c r="B4" t="n">
-        <v>91180</v>
+        <v>91166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591392</v>
+        <v>591502</v>
       </c>
       <c r="R4" t="n">
-        <v>6931082</v>
+        <v>6931244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125528826</v>
+        <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591502</v>
+        <v>591392</v>
       </c>
       <c r="R5" t="n">
-        <v>6931244</v>
+        <v>6931082</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125528795</v>
+        <v>125528826</v>
       </c>
       <c r="B3" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125528826</v>
+        <v>125528795</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,12 +969,7 @@
         <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125528826</v>
       </c>
       <c r="B3" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125528795</v>
       </c>
       <c r="B4" t="n">
-        <v>88626</v>
+        <v>88633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125528826</v>
       </c>
       <c r="B3" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125528795</v>
       </c>
       <c r="B4" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125528826</v>
       </c>
       <c r="B3" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125528795</v>
       </c>
       <c r="B4" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125528826</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125528795</v>
       </c>
       <c r="B4" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27556-2021 artfynd.xlsx
+++ b/artfynd/A 27556-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125528663</v>
       </c>
       <c r="B2" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125528826</v>
       </c>
       <c r="B3" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125528795</v>
       </c>
       <c r="B4" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125529623</v>
       </c>
       <c r="B5" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
